--- a/data/output/2025/evaluasi_76.xlsx
+++ b/data/output/2025/evaluasi_76.xlsx
@@ -1765,7 +1765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2105,6 +2105,230 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8.539730064197531</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4492078740743019</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.462656681238615</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0192616011973378</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.517586587257065</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.08493772552672707</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.694676365474513</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2305,18 +2529,298 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>0.2957047684341121</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>37.59923332919774</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.537598504415667</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9.231415474290394</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.562415237866584</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.061152595209632</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.04013584439640647</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.6307785248627709</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.182825122011635</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7603</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamasa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>-4.552352839243981</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2333,7 +2837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2631,20 +3135,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-8.79659813071626</v>
+        <v>0.06540484981584745</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2659,18 +3163,326 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>29.58904506716207</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.482089226303055</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-9.944665651442621</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.63681628334773</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-3.584497111219462</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-16.0949880346407</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.137690323707196</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.654837718115575</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2.634826000551955</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-8.79659813071626</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>-6.907248137256619</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2687,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,6 +3671,370 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.053919312103996</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>37.12255346417933</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-7.71482779199764</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.04651279409298</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-11.17073774503586</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9209514418237825</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-3.02474091049309</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-8.1934952698795</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.558743384384853</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.465914596296077</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.6705048753125794</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.707372523667837</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2873,7 +4049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3129,6 +4305,230 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32.41564082528777</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.350518234456924</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.154150122628865</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.740126728482953</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3004512844249191</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.9757001335025229</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7601</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Majene</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.410225108837311</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3143,7 +4543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3374,6 +4774,286 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1172813366127135</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.60565201906277</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.249029954402114</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7923976945902932</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.92724633306429</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.068260594944558</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.072408127528158</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5113199747099267</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2.508456855766921</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
